--- a/design_tables/excel/EnemyAction.xlsx
+++ b/design_tables/excel/EnemyAction.xlsx
@@ -152,22 +152,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EnemyActionTable" displayName="EnemyActionTable" ref="A1:H6" headerRowCount="1">
-  <tableColumns count="8">
-    <tableColumn id="1" name="id"/>
-    <tableColumn id="2" name="name"/>
-    <tableColumn id="3" name="action_type"/>
-    <tableColumn id="4" name="target"/>
-    <tableColumn id="5" name="intent_type"/>
-    <tableColumn id="6" name="effect_ids"/>
-    <tableColumn id="7" name="intent_description"/>
-    <tableColumn id="8" name="comment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,7 +459,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -511,7 +495,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -547,7 +531,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -570,8 +554,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>